--- a/artfynd/A 61231-2025 artfynd.xlsx
+++ b/artfynd/A 61231-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1020,6 +1020,1490 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>130803168</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57862</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Nordfjället, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>465993</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7072380</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>130803173</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57862</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Nordfjället, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>466010</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7072292</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>130803176</v>
+      </c>
+      <c r="B7" t="n">
+        <v>91794</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Nordfjället, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>466028</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7072541</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>130803170</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57862</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Nordfjället, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>465964</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7072357</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>130803180</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79219</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Nordfjället, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>466202</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7072689</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>130803181</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79219</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Nordfjället, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>466203</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7072486</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>130803175</v>
+      </c>
+      <c r="B11" t="n">
+        <v>91770</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Nordfjället, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>466080</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7072573</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>130803178</v>
+      </c>
+      <c r="B12" t="n">
+        <v>91794</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Nordfjället, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>466018</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7072336</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>130803165</v>
+      </c>
+      <c r="B13" t="n">
+        <v>92496</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Nordfjället, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>466019</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7072412</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>130803166</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57862</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Nordfjället, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>466057</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7072377</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>130803167</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57862</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Nordfjället, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>465963</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7072446</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>130803172</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57862</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Nordfjället, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>465981</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7072327</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>130803179</v>
+      </c>
+      <c r="B17" t="n">
+        <v>91794</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Nordfjället, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>466062</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7072360</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>130803169</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57862</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Nordfjället, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>465965</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7072357</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>130803177</v>
+      </c>
+      <c r="B19" t="n">
+        <v>91794</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Nordfjället, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>465951</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7072435</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 61231-2025 artfynd.xlsx
+++ b/artfynd/A 61231-2025 artfynd.xlsx
@@ -1023,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130803168</v>
+        <v>130803173</v>
       </c>
       <c r="B5" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1058,10 +1058,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>465993</v>
+        <v>466010</v>
       </c>
       <c r="R5" t="n">
-        <v>7072380</v>
+        <v>7072292</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,7 +1098,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1125,10 +1125,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130803173</v>
+        <v>130803168</v>
       </c>
       <c r="B6" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1160,10 +1160,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>466010</v>
+        <v>465993</v>
       </c>
       <c r="R6" t="n">
-        <v>7072292</v>
+        <v>7072380</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1227,10 +1227,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130803176</v>
+        <v>130803170</v>
       </c>
       <c r="B7" t="n">
-        <v>91794</v>
+        <v>57863</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1238,19 +1238,23 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1258,10 +1262,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466028</v>
+        <v>465964</v>
       </c>
       <c r="R7" t="n">
-        <v>7072541</v>
+        <v>7072357</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1294,6 +1298,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1320,10 +1329,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130803170</v>
+        <v>130803176</v>
       </c>
       <c r="B8" t="n">
-        <v>57862</v>
+        <v>91795</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1331,23 +1340,19 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1355,10 +1360,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>465964</v>
+        <v>466028</v>
       </c>
       <c r="R8" t="n">
-        <v>7072357</v>
+        <v>7072541</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1391,11 +1396,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-01-20</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1425,7 +1425,7 @@
         <v>130803180</v>
       </c>
       <c r="B9" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
         <v>130803181</v>
       </c>
       <c r="B10" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
         <v>130803175</v>
       </c>
       <c r="B11" t="n">
-        <v>91770</v>
+        <v>91771</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>130803178</v>
       </c>
       <c r="B12" t="n">
-        <v>91794</v>
+        <v>91795</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1816,32 +1816,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130803165</v>
+        <v>130803167</v>
       </c>
       <c r="B13" t="n">
-        <v>92496</v>
+        <v>57863</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1851,10 +1851,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>466019</v>
+        <v>465963</v>
       </c>
       <c r="R13" t="n">
-        <v>7072412</v>
+        <v>7072446</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1887,6 +1887,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1916,7 +1921,7 @@
         <v>130803166</v>
       </c>
       <c r="B14" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2015,32 +2020,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130803167</v>
+        <v>130803165</v>
       </c>
       <c r="B15" t="n">
-        <v>57862</v>
+        <v>92497</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2050,10 +2055,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>465963</v>
+        <v>466019</v>
       </c>
       <c r="R15" t="n">
-        <v>7072446</v>
+        <v>7072412</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2086,11 +2091,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-01-20</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2120,7 +2120,7 @@
         <v>130803172</v>
       </c>
       <c r="B16" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         <v>130803179</v>
       </c>
       <c r="B17" t="n">
-        <v>91794</v>
+        <v>91795</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2312,10 +2312,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130803169</v>
+        <v>130803177</v>
       </c>
       <c r="B18" t="n">
-        <v>57862</v>
+        <v>91795</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2323,23 +2323,19 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2347,10 +2343,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>465965</v>
+        <v>465951</v>
       </c>
       <c r="R18" t="n">
-        <v>7072357</v>
+        <v>7072435</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2383,11 +2379,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-01-20</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2414,10 +2405,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130803177</v>
+        <v>130803169</v>
       </c>
       <c r="B19" t="n">
-        <v>91794</v>
+        <v>57863</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2425,19 +2416,23 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2445,10 +2440,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>465951</v>
+        <v>465965</v>
       </c>
       <c r="R19" t="n">
-        <v>7072435</v>
+        <v>7072357</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2481,6 +2476,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 61231-2025 artfynd.xlsx
+++ b/artfynd/A 61231-2025 artfynd.xlsx
@@ -1023,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130803173</v>
+        <v>130803168</v>
       </c>
       <c r="B5" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1058,10 +1058,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>466010</v>
+        <v>465993</v>
       </c>
       <c r="R5" t="n">
-        <v>7072292</v>
+        <v>7072380</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,7 +1098,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1125,10 +1125,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130803168</v>
+        <v>130803173</v>
       </c>
       <c r="B6" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1160,10 +1160,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>465993</v>
+        <v>466010</v>
       </c>
       <c r="R6" t="n">
-        <v>7072380</v>
+        <v>7072292</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1227,10 +1227,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130803170</v>
+        <v>130803176</v>
       </c>
       <c r="B7" t="n">
-        <v>57863</v>
+        <v>91796</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1238,23 +1238,19 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1262,10 +1258,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>465964</v>
+        <v>466028</v>
       </c>
       <c r="R7" t="n">
-        <v>7072357</v>
+        <v>7072541</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1298,11 +1294,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-01-20</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1329,10 +1320,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130803176</v>
+        <v>130803170</v>
       </c>
       <c r="B8" t="n">
-        <v>91795</v>
+        <v>57864</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1340,19 +1331,23 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1360,10 +1355,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466028</v>
+        <v>465964</v>
       </c>
       <c r="R8" t="n">
-        <v>7072541</v>
+        <v>7072357</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1396,6 +1391,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1425,7 +1425,7 @@
         <v>130803180</v>
       </c>
       <c r="B9" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
         <v>130803181</v>
       </c>
       <c r="B10" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
         <v>130803175</v>
       </c>
       <c r="B11" t="n">
-        <v>91771</v>
+        <v>91772</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>130803178</v>
       </c>
       <c r="B12" t="n">
-        <v>91795</v>
+        <v>91796</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1816,10 +1816,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130803167</v>
+        <v>130803166</v>
       </c>
       <c r="B13" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1851,10 +1851,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>465963</v>
+        <v>466057</v>
       </c>
       <c r="R13" t="n">
-        <v>7072446</v>
+        <v>7072377</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1891,7 +1891,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1918,10 +1918,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130803166</v>
+        <v>130803167</v>
       </c>
       <c r="B14" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1953,10 +1953,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>466057</v>
+        <v>465963</v>
       </c>
       <c r="R14" t="n">
-        <v>7072377</v>
+        <v>7072446</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1993,7 +1993,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2023,7 +2023,7 @@
         <v>130803165</v>
       </c>
       <c r="B15" t="n">
-        <v>92497</v>
+        <v>92498</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>130803172</v>
       </c>
       <c r="B16" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         <v>130803179</v>
       </c>
       <c r="B17" t="n">
-        <v>91795</v>
+        <v>91796</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>130803177</v>
       </c>
       <c r="B18" t="n">
-        <v>91795</v>
+        <v>91796</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2408,7 +2408,7 @@
         <v>130803169</v>
       </c>
       <c r="B19" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 61231-2025 artfynd.xlsx
+++ b/artfynd/A 61231-2025 artfynd.xlsx
@@ -1816,32 +1816,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130803166</v>
+        <v>130803165</v>
       </c>
       <c r="B13" t="n">
-        <v>57864</v>
+        <v>92498</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1851,10 +1851,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>466057</v>
+        <v>466019</v>
       </c>
       <c r="R13" t="n">
-        <v>7072377</v>
+        <v>7072412</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1887,11 +1887,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-01-20</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1918,7 +1913,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130803167</v>
+        <v>130803166</v>
       </c>
       <c r="B14" t="n">
         <v>57864</v>
@@ -1953,10 +1948,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>465963</v>
+        <v>466057</v>
       </c>
       <c r="R14" t="n">
-        <v>7072446</v>
+        <v>7072377</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1993,7 +1988,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2020,32 +2015,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130803165</v>
+        <v>130803167</v>
       </c>
       <c r="B15" t="n">
-        <v>92498</v>
+        <v>57864</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2055,10 +2050,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>466019</v>
+        <v>465963</v>
       </c>
       <c r="R15" t="n">
-        <v>7072412</v>
+        <v>7072446</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2091,6 +2086,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 61231-2025 artfynd.xlsx
+++ b/artfynd/A 61231-2025 artfynd.xlsx
@@ -1816,32 +1816,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130803165</v>
+        <v>130803166</v>
       </c>
       <c r="B13" t="n">
-        <v>92498</v>
+        <v>57864</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1851,10 +1851,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>466019</v>
+        <v>466057</v>
       </c>
       <c r="R13" t="n">
-        <v>7072412</v>
+        <v>7072377</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1887,6 +1887,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1913,7 +1918,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130803166</v>
+        <v>130803167</v>
       </c>
       <c r="B14" t="n">
         <v>57864</v>
@@ -1948,10 +1953,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>466057</v>
+        <v>465963</v>
       </c>
       <c r="R14" t="n">
-        <v>7072377</v>
+        <v>7072446</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1988,7 +1993,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2015,32 +2020,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130803167</v>
+        <v>130803165</v>
       </c>
       <c r="B15" t="n">
-        <v>57864</v>
+        <v>92498</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2050,10 +2055,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>465963</v>
+        <v>466019</v>
       </c>
       <c r="R15" t="n">
-        <v>7072446</v>
+        <v>7072412</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2086,11 +2091,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-01-20</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2312,10 +2312,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130803177</v>
+        <v>130803169</v>
       </c>
       <c r="B18" t="n">
-        <v>91796</v>
+        <v>57864</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2323,19 +2323,23 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2343,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>465951</v>
+        <v>465965</v>
       </c>
       <c r="R18" t="n">
-        <v>7072435</v>
+        <v>7072357</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2379,6 +2383,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2405,10 +2414,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130803169</v>
+        <v>130803177</v>
       </c>
       <c r="B19" t="n">
-        <v>57864</v>
+        <v>91796</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2416,23 +2425,19 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2440,10 +2445,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>465965</v>
+        <v>465951</v>
       </c>
       <c r="R19" t="n">
-        <v>7072357</v>
+        <v>7072435</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2476,11 +2481,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-01-20</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 61231-2025 artfynd.xlsx
+++ b/artfynd/A 61231-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>89597425</v>
+        <v>130803175</v>
       </c>
       <c r="B2" t="n">
-        <v>85703</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>510</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>S Lill-Veksjön, Lill-Bakvattnet, Tretjärnarna, Jmt</t>
+          <t>Nordfjället, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>466324.8371589889</v>
+        <v>466080</v>
       </c>
       <c r="R2" t="n">
-        <v>7072600.156397815</v>
+        <v>7072573</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-09-18</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-09-18</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,31 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>89597423</v>
+        <v>130803165</v>
       </c>
       <c r="B3" t="n">
-        <v>90074</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -827,14 +803,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>S Lill-Veksjön, Lill-Bakvattnet, Tretjärnarna, Jmt</t>
+          <t>Nordfjället, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>466379.7973726752</v>
+        <v>466019</v>
       </c>
       <c r="R3" t="n">
-        <v>7072687.142694952</v>
+        <v>7072412</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,22 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2020-09-18</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2020-09-18</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,66 +857,57 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>89597424</v>
+        <v>130803180</v>
       </c>
       <c r="B4" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>S Lill-Veksjön, Lill-Bakvattnet, Tretjärnarna, Jmt</t>
+          <t>Nordfjället, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>466330.0062436588</v>
+        <v>466202</v>
       </c>
       <c r="R4" t="n">
-        <v>7072627.965735061</v>
+        <v>7072689</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,22 +934,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2020-09-18</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2020-09-18</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1007,48 +959,44 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130803168</v>
+        <v>130803181</v>
       </c>
       <c r="B5" t="n">
-        <v>57884</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1058,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>465993</v>
+        <v>466203</v>
       </c>
       <c r="R5" t="n">
-        <v>7072380</v>
+        <v>7072486</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,7 +1046,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1125,10 +1073,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130803173</v>
+        <v>130803166</v>
       </c>
       <c r="B6" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1160,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>466010</v>
+        <v>466057</v>
       </c>
       <c r="R6" t="n">
-        <v>7072292</v>
+        <v>7072377</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,7 +1148,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1227,10 +1175,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130803170</v>
+        <v>130803167</v>
       </c>
       <c r="B7" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1262,10 +1210,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>465964</v>
+        <v>465963</v>
       </c>
       <c r="R7" t="n">
-        <v>7072357</v>
+        <v>7072446</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1302,7 +1250,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1329,10 +1277,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130803176</v>
+        <v>130803168</v>
       </c>
       <c r="B8" t="n">
-        <v>91828</v>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1340,19 +1288,23 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1360,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466028</v>
+        <v>465993</v>
       </c>
       <c r="R8" t="n">
-        <v>7072541</v>
+        <v>7072380</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1396,6 +1348,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1422,10 +1379,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130803180</v>
+        <v>130803169</v>
       </c>
       <c r="B9" t="n">
-        <v>79243</v>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1433,21 +1390,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1457,10 +1414,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>466202</v>
+        <v>465965</v>
       </c>
       <c r="R9" t="n">
-        <v>7072689</v>
+        <v>7072357</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1497,7 +1454,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1524,10 +1481,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130803181</v>
+        <v>130803170</v>
       </c>
       <c r="B10" t="n">
-        <v>79243</v>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1535,21 +1492,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1559,10 +1516,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466203</v>
+        <v>465964</v>
       </c>
       <c r="R10" t="n">
-        <v>7072486</v>
+        <v>7072357</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1599,7 +1556,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1626,10 +1583,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130803175</v>
+        <v>130803171</v>
       </c>
       <c r="B11" t="n">
-        <v>91804</v>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1637,21 +1594,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1661,10 +1618,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466080</v>
+        <v>465963</v>
       </c>
       <c r="R11" t="n">
-        <v>7072573</v>
+        <v>7072339</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1697,6 +1654,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1723,10 +1685,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130803178</v>
+        <v>130803172</v>
       </c>
       <c r="B12" t="n">
-        <v>91828</v>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1734,19 +1696,23 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1754,10 +1720,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466018</v>
+        <v>465981</v>
       </c>
       <c r="R12" t="n">
-        <v>7072336</v>
+        <v>7072327</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1790,6 +1756,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1816,32 +1787,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130803165</v>
+        <v>130803173</v>
       </c>
       <c r="B13" t="n">
-        <v>92530</v>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1851,10 +1822,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>466019</v>
+        <v>466010</v>
       </c>
       <c r="R13" t="n">
-        <v>7072412</v>
+        <v>7072292</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1887,6 +1858,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1913,10 +1889,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130803166</v>
+        <v>130803174</v>
       </c>
       <c r="B14" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1948,10 +1924,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>466057</v>
+        <v>466016</v>
       </c>
       <c r="R14" t="n">
-        <v>7072377</v>
+        <v>7072284</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2015,10 +1991,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130803167</v>
+        <v>89597425</v>
       </c>
       <c r="B15" t="n">
-        <v>57884</v>
+        <v>89292</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2026,34 +2002,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Nordfjället, Jmt</t>
+          <t>S Lill-Veksjön, Lill-Bakvattnet, Tretjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>465963</v>
+        <v>466325</v>
       </c>
       <c r="R15" t="n">
-        <v>7072446</v>
+        <v>7072600</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2080,17 +2056,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2020-09-18</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2020-09-18</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2105,57 +2076,61 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130803172</v>
+        <v>89597423</v>
       </c>
       <c r="B16" t="n">
-        <v>57884</v>
+        <v>92632</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Nordfjället, Jmt</t>
+          <t>S Lill-Veksjön, Lill-Bakvattnet, Tretjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>465981</v>
+        <v>466380</v>
       </c>
       <c r="R16" t="n">
-        <v>7072327</v>
+        <v>7072687</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2182,17 +2157,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2020-09-18</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+          <t>2020-09-18</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2207,22 +2177,26 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130803179</v>
+        <v>89597424</v>
       </c>
       <c r="B17" t="n">
-        <v>91828</v>
+        <v>83307</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2230,30 +2204,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Nordfjället, Jmt</t>
+          <t>S Lill-Veksjön, Lill-Bakvattnet, Tretjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>466062</v>
+        <v>466330</v>
       </c>
       <c r="R17" t="n">
-        <v>7072360</v>
+        <v>7072628</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2280,12 +2258,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2020-09-18</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2020-09-18</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2300,22 +2278,26 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130803177</v>
+        <v>89597426</v>
       </c>
       <c r="B18" t="n">
-        <v>91828</v>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2323,30 +2305,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Nordfjället, Jmt</t>
+          <t>S Lill-Veksjön, Lill-Bakvattnet, Tretjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>465951</v>
+        <v>466350</v>
       </c>
       <c r="R18" t="n">
-        <v>7072435</v>
+        <v>7072653</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2373,12 +2359,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2020-09-18</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2020-09-18</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2393,57 +2384,61 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130803169</v>
+        <v>89597419</v>
       </c>
       <c r="B19" t="n">
-        <v>57884</v>
+        <v>57141</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Nordfjället, Jmt</t>
+          <t>S Lill-Veksjön, Lill-Bakvattnet, Tretjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>465965</v>
+        <v>466323</v>
       </c>
       <c r="R19" t="n">
-        <v>7072357</v>
+        <v>7072599</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2470,17 +2465,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2020-09-18</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2020-09-18</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2495,15 +2485,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 61231-2025 artfynd.xlsx
+++ b/artfynd/A 61231-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89597425</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130803175</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -971,6 +986,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89597423</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1068,6 +1088,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130803165</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1170,6 +1195,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130803180</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1272,6 +1302,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130803181</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1373,6 +1408,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89597424</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1479,6 +1519,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89597426</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1581,6 +1626,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130803166</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1683,6 +1733,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130803167</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1785,6 +1840,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130803168</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1887,6 +1947,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130803169</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1989,6 +2054,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130803170</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2091,6 +2161,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130803171</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2193,6 +2268,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130803172</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2295,6 +2375,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130803173</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2397,6 +2482,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130803174</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2498,8 +2588,33 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89597419</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>